--- a/data/rules.xlsx
+++ b/data/rules.xlsx
@@ -452,7 +452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -882,6 +882,90 @@
         </is>
       </c>
     </row>
+    <row r="11" ht="18" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>NSVC</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>발생 일수</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>&gt;=</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>3일</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>NSVC 지속 발생 → 환경 또는 단말 점검 필요</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>복합</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>3일 이상 지속 시 (OR 조건)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>NSVC</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>LEV3 이상 (LEV3/LEV4/LEV5)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>&gt;</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>LEV3 이상 발생 → 환경 또는 단말 점검 필요</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>단순</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>LEV3/LEV4/LEV5 중 하나라도 발생 시 (OR 조건)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
